--- a/Product List for Vipul.xlsx
+++ b/Product List for Vipul.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8d857f4fd2d1f3c9/Desktop/vipul-workspace/Pestxz/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="31" documentId="11_D40BF1EFD0C97F24BBB18800E42C356DF1B3CF52" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F3E5B647-13B3-4270-9804-090D7E74D7A8}"/>
+  <xr:revisionPtr revIDLastSave="34" documentId="11_D40BF1EFD0C97F24BBB18800E42C356DF1B3CF52" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F986779D-688C-44DE-B90B-0B9C5141AF7F}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10548" yWindow="0" windowWidth="12588" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -196,7 +196,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -269,15 +269,49 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -287,6 +321,10 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -296,10 +334,15 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -583,7 +626,7 @@
   <dimension ref="A1:K25"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="55" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.109375" customWidth="1"/>
     <col min="3" max="3" width="13.88671875" customWidth="1"/>
     <col min="4" max="4" width="12.77734375" customWidth="1"/>
@@ -594,535 +637,536 @@
     <col min="10" max="10" width="10.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:11" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-    </row>
-    <row r="2" spans="1:11" s="9" customFormat="1" ht="27" x14ac:dyDescent="0.3">
-      <c r="A2" s="5" t="s">
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="11"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+    </row>
+    <row r="2" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="D2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="E2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="F2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="8" t="s">
+      <c r="G2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="H2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="8" t="s">
+      <c r="I2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="8" t="s">
+      <c r="J2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="8"/>
+      <c r="K2" s="4"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A3" s="6"/>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="4" t="s">
+      <c r="A3" s="7"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="H3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="I3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="J3" s="3"/>
-      <c r="K3" s="3"/>
-    </row>
-    <row r="4" spans="1:11" ht="27" x14ac:dyDescent="0.3">
-      <c r="A4" s="6"/>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="4" t="s">
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A4" s="7"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="G4" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="H4" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="I4" s="4" t="s">
+      <c r="I4" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="J4" s="3"/>
-      <c r="K4" s="3"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A5" s="7"/>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J5" s="3"/>
-      <c r="K5" s="3"/>
-    </row>
-    <row r="6" spans="1:11" s="9" customFormat="1" ht="27" x14ac:dyDescent="0.3">
-      <c r="A6" s="5" t="s">
+      <c r="A5" s="8"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
+    </row>
+    <row r="6" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="E6" s="8" t="s">
+      <c r="E6" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="F6" s="8" t="s">
+      <c r="F6" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="G6" s="8" t="s">
+      <c r="G6" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H6" s="8" t="s">
+      <c r="H6" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="I6" s="8" t="s">
+      <c r="I6" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="J6" s="8" t="s">
+      <c r="J6" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="K6" s="8"/>
+      <c r="K6" s="4"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A7" s="6"/>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="4" t="s">
+      <c r="A7" s="7"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="G7" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H7" s="4" t="s">
+      <c r="H7" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="I7" s="3"/>
-      <c r="J7" s="3"/>
-      <c r="K7" s="3"/>
-    </row>
-    <row r="8" spans="1:11" ht="40.200000000000003" x14ac:dyDescent="0.3">
-      <c r="A8" s="6"/>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="4" t="s">
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="2"/>
+    </row>
+    <row r="8" spans="1:11" ht="27" x14ac:dyDescent="0.3">
+      <c r="A8" s="7"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="G8" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="H8" s="4" t="s">
+      <c r="H8" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="I8" s="3"/>
-      <c r="J8" s="3"/>
-      <c r="K8" s="3"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="2"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A9" s="6"/>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="H9" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="I9" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J9" s="3"/>
-      <c r="K9" s="3"/>
-    </row>
-    <row r="10" spans="1:11" s="9" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="5" t="s">
+      <c r="A9" s="7"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2"/>
+    </row>
+    <row r="10" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="C10" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="D10" s="8" t="s">
+      <c r="D10" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="E10" s="8" t="s">
+      <c r="E10" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="F10" s="8" t="s">
+      <c r="F10" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="G10" s="8" t="s">
+      <c r="G10" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="H10" s="8"/>
-      <c r="I10" s="8"/>
-      <c r="J10" s="8"/>
-      <c r="K10" s="8"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="4"/>
+      <c r="K10" s="4"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A11" s="6"/>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="4" t="s">
+      <c r="A11" s="7"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="F11" s="4" t="s">
+      <c r="F11" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
-      <c r="J11" s="3"/>
-      <c r="K11" s="3"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="2"/>
+      <c r="K11" s="2"/>
     </row>
     <row r="12" spans="1:11" ht="40.200000000000003" x14ac:dyDescent="0.3">
-      <c r="A12" s="6"/>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="4" t="s">
+      <c r="A12" s="7"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="F12" s="4" t="s">
+      <c r="F12" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
-      <c r="J12" s="3"/>
-      <c r="K12" s="3"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+      <c r="K12" s="2"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A13" s="7"/>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
-      <c r="J13" s="3"/>
-      <c r="K13" s="3"/>
-    </row>
-    <row r="14" spans="1:11" s="9" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="5" t="s">
+      <c r="A13" s="8"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
+      <c r="K13" s="2"/>
+    </row>
+    <row r="14" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="B14" s="8" t="s">
+      <c r="B14" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C14" s="8" t="s">
+      <c r="C14" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="D14" s="8" t="s">
+      <c r="D14" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="E14" s="8" t="s">
+      <c r="E14" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="F14" s="8" t="s">
+      <c r="F14" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="G14" s="8" t="s">
+      <c r="G14" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="H14" s="8"/>
-      <c r="I14" s="8"/>
-      <c r="J14" s="8"/>
-      <c r="K14" s="8"/>
+      <c r="H14" s="4"/>
+      <c r="I14" s="4"/>
+      <c r="J14" s="4"/>
+      <c r="K14" s="4"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A15" s="6"/>
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="4" t="s">
+      <c r="A15" s="7"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="F15" s="4" t="s">
+      <c r="F15" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
-      <c r="J15" s="3"/>
-      <c r="K15" s="3"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
+      <c r="K15" s="2"/>
     </row>
     <row r="16" spans="1:11" ht="40.200000000000003" x14ac:dyDescent="0.3">
-      <c r="A16" s="6"/>
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="4" t="s">
+      <c r="A16" s="7"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="F16" s="4" t="s">
+      <c r="F16" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
-      <c r="J16" s="3"/>
-      <c r="K16" s="3"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
+      <c r="K16" s="2"/>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A17" s="7"/>
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="G17" s="3"/>
-      <c r="H17" s="3"/>
-      <c r="I17" s="3"/>
-      <c r="J17" s="3"/>
-      <c r="K17" s="3"/>
-    </row>
-    <row r="18" spans="1:11" s="9" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="5" t="s">
+      <c r="A17" s="8"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="2"/>
+      <c r="K17" s="2"/>
+    </row>
+    <row r="18" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B18" s="8" t="s">
+      <c r="B18" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C18" s="8" t="s">
+      <c r="C18" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="D18" s="8" t="s">
+      <c r="D18" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="E18" s="8" t="s">
+      <c r="E18" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="F18" s="8" t="s">
+      <c r="F18" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="G18" s="8" t="s">
+      <c r="G18" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="H18" s="8"/>
-      <c r="I18" s="8"/>
-      <c r="J18" s="8"/>
-      <c r="K18" s="8"/>
+      <c r="H18" s="4"/>
+      <c r="I18" s="4"/>
+      <c r="J18" s="4"/>
+      <c r="K18" s="4"/>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A19" s="6"/>
-      <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
-      <c r="E19" s="4" t="s">
+      <c r="A19" s="7"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="F19" s="4" t="s">
+      <c r="F19" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="G19" s="3" t="s">
+      <c r="G19" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="H19" s="3"/>
-      <c r="I19" s="3"/>
-      <c r="J19" s="3"/>
-      <c r="K19" s="3"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="2"/>
+      <c r="K19" s="2"/>
     </row>
     <row r="20" spans="1:11" ht="40.200000000000003" x14ac:dyDescent="0.3">
-      <c r="A20" s="6"/>
-      <c r="B20" s="3"/>
-      <c r="C20" s="3"/>
-      <c r="D20" s="3"/>
-      <c r="E20" s="4" t="s">
+      <c r="A20" s="7"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="F20" s="4" t="s">
+      <c r="F20" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="G20" s="3"/>
-      <c r="H20" s="3"/>
-      <c r="I20" s="3"/>
-      <c r="J20" s="3"/>
-      <c r="K20" s="3"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="2"/>
+      <c r="K20" s="2"/>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A21" s="7"/>
-      <c r="B21" s="3"/>
-      <c r="C21" s="3"/>
-      <c r="D21" s="3"/>
-      <c r="E21" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="F21" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="G21" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="H21" s="3"/>
-      <c r="I21" s="3"/>
-      <c r="J21" s="3"/>
-      <c r="K21" s="3"/>
-    </row>
-    <row r="22" spans="1:11" s="9" customFormat="1" ht="27" x14ac:dyDescent="0.3">
-      <c r="A22" s="5" t="s">
+      <c r="A21" s="8"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
+      <c r="J21" s="2"/>
+      <c r="K21" s="2"/>
+    </row>
+    <row r="22" spans="1:11" s="5" customFormat="1" ht="27" x14ac:dyDescent="0.3">
+      <c r="A22" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="B22" s="8" t="s">
+      <c r="B22" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C22" s="8" t="s">
+      <c r="C22" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="D22" s="8" t="s">
+      <c r="D22" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="E22" s="8" t="s">
+      <c r="E22" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="F22" s="8" t="s">
+      <c r="F22" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="G22" s="8" t="s">
+      <c r="G22" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="H22" s="8"/>
-      <c r="I22" s="8"/>
-      <c r="J22" s="8"/>
-      <c r="K22" s="8"/>
+      <c r="H22" s="4"/>
+      <c r="I22" s="4"/>
+      <c r="J22" s="4"/>
+      <c r="K22" s="4"/>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A23" s="6"/>
-      <c r="B23" s="3"/>
-      <c r="C23" s="3"/>
-      <c r="D23" s="3"/>
-      <c r="E23" s="4" t="s">
+      <c r="A23" s="7"/>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="F23" s="4" t="s">
+      <c r="F23" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="G23" s="3" t="s">
+      <c r="G23" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="H23" s="3"/>
-      <c r="I23" s="3"/>
-      <c r="J23" s="3"/>
-      <c r="K23" s="3"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="2"/>
+      <c r="K23" s="2"/>
     </row>
     <row r="24" spans="1:11" ht="40.200000000000003" x14ac:dyDescent="0.3">
-      <c r="A24" s="6"/>
-      <c r="B24" s="3"/>
-      <c r="C24" s="3"/>
-      <c r="D24" s="3"/>
-      <c r="E24" s="4" t="s">
+      <c r="A24" s="7"/>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="F24" s="3"/>
-      <c r="G24" s="3"/>
-      <c r="H24" s="3"/>
-      <c r="I24" s="3"/>
-      <c r="J24" s="3"/>
-      <c r="K24" s="3"/>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+      <c r="J24" s="2"/>
+      <c r="K24" s="2"/>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A25" s="7"/>
-      <c r="B25" s="3"/>
-      <c r="C25" s="3"/>
-      <c r="D25" s="3"/>
-      <c r="E25" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="F25" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="G25" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="H25" s="3"/>
-      <c r="I25" s="3"/>
-      <c r="J25" s="3"/>
-      <c r="K25" s="3"/>
+      <c r="A25" s="8"/>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H25" s="2"/>
+      <c r="I25" s="2"/>
+      <c r="J25" s="2"/>
+      <c r="K25" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="7">
+    <mergeCell ref="A22:A25"/>
+    <mergeCell ref="A1:I1"/>
     <mergeCell ref="A2:A5"/>
     <mergeCell ref="A6:A9"/>
     <mergeCell ref="A10:A13"/>
     <mergeCell ref="A14:A17"/>
     <mergeCell ref="A18:A21"/>
-    <mergeCell ref="A22:A25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
